--- a/docs/planilhas/Planilha_Testes_Verzel_Store.xlsx
+++ b/docs/planilhas/Planilha_Testes_Verzel_Store.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="635">
   <si>
     <t>Resumo da execução</t>
   </si>
@@ -480,6 +480,9 @@
     <t>8 produtos com id, nome, descricao, categoria, preco; preços conforme tabela</t>
   </si>
   <si>
+    <t>Relatório Playwright</t>
+  </si>
+  <si>
     <t>API-02</t>
   </si>
   <si>
@@ -495,6 +498,9 @@
     <t>Produto P001, Camiseta Essencial, preco 59.9</t>
   </si>
   <si>
+    <t xml:space="preserve">	 Passou</t>
+  </si>
+  <si>
     <t>API-03</t>
   </si>
   <si>
@@ -1056,6 +1062,12 @@
     <t>Subtotal 100,00 | Desconto 10,00 | Frete 19,90 | Faltante 100,00 | Total 109,90</t>
   </si>
   <si>
+    <t xml:space="preserve">passou </t>
+  </si>
+  <si>
+    <t>aceita</t>
+  </si>
+  <si>
     <t>CT-A2a</t>
   </si>
   <si>
@@ -1071,12 +1083,6 @@
     <t>Desconto 10,00 | Total 109,90</t>
   </si>
   <si>
-    <t xml:space="preserve">passou </t>
-  </si>
-  <si>
-    <t>aceita</t>
-  </si>
-  <si>
     <t>CT-A2b</t>
   </si>
   <si>
@@ -1182,7 +1188,7 @@
     <t>Clicar em aplicar sem digitar</t>
   </si>
   <si>
-    <t>Nada é aplicado; mensagem clara (anotar). Não deve quebrar a tela.</t>
+    <t>Nada é aplicado; mensagem clara (Informe um cupom). Não deve quebrar a tela.</t>
   </si>
   <si>
     <t>Aplicar cupom antes de adicionar produto</t>
@@ -1263,6 +1269,10 @@
     <t>Frete 19,90 | Aviso: faltam R$ 100,00 | Total 119,90</t>
   </si>
   <si>
+    <t xml:space="preserve">aceita
+</t>
+  </si>
+  <si>
     <t>CT-B4</t>
   </si>
   <si>
@@ -1341,7 +1351,7 @@
     <t>Adicionar 5× Garrafa Térmica</t>
   </si>
   <si>
-    <t>Aceita | Subtotal 250,00 | Frete 0,00 | Total 250,00</t>
+    <t xml:space="preserve">Aceita | Subtotal 250,00 | Frete 0,00 | Total  250,00 </t>
   </si>
   <si>
     <t>CT-C2a</t>
@@ -1527,6 +1537,9 @@
     <t>Rejeita com mensagem no campo</t>
   </si>
   <si>
+    <t>Rejeita</t>
+  </si>
+  <si>
     <t>CT-E4</t>
   </si>
   <si>
@@ -1536,9 +1549,6 @@
     <t>Deixar nome em branco</t>
   </si>
   <si>
-    <t>Rejeita</t>
-  </si>
-  <si>
     <t>Nome com espaço no fim (ambiguidade)</t>
   </si>
   <si>
@@ -1579,6 +1589,11 @@
   </si>
   <si>
     <t>Testar: 0131010 (7) | 013101000 (9) | abcde-fgh | vazio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falhou
+Falhou
+</t>
   </si>
   <si>
     <t>CT-E10</t>
@@ -1927,7 +1942,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1940,6 +1955,12 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -2063,7 +2084,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="49">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2071,20 +2092,14 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2092,7 +2107,13 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -2101,115 +2122,112 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="8" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="6" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="7" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="7" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="9" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="10" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="5" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="6" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2523,126 +2541,126 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5">
       <c r="A1" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="B1" s="29"/>
+        <v>610</v>
+      </c>
+      <c r="B1" s="28"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29"/>
+      <c r="A2" s="27"/>
+      <c r="B2" s="28"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="46" t="s">
-        <v>607</v>
-      </c>
-      <c r="B3" s="46" t="s">
-        <v>608</v>
+      <c r="A3" s="45" t="s">
+        <v>611</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>612</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="28" t="s">
-        <v>609</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>610</v>
+      <c r="A4" s="27" t="s">
+        <v>613</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>614</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="29" t="s">
-        <v>611</v>
+      <c r="B5" s="28" t="s">
+        <v>615</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="29" t="s">
-        <v>612</v>
+      <c r="B6" s="28" t="s">
+        <v>616</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="28" t="s">
-        <v>613</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>614</v>
+      <c r="A7" s="27" t="s">
+        <v>617</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>618</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="28" t="s">
-        <v>615</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>616</v>
+      <c r="A8" s="27" t="s">
+        <v>619</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>620</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="28" t="s">
-        <v>617</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>618</v>
+      <c r="A9" s="27" t="s">
+        <v>621</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>622</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="28" t="s">
-        <v>619</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>620</v>
+      <c r="A10" s="27" t="s">
+        <v>623</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>624</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="28"/>
-      <c r="B11" s="29"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="28"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="46" t="s">
-        <v>621</v>
-      </c>
-      <c r="B12" s="47"/>
+      <c r="A12" s="45" t="s">
+        <v>625</v>
+      </c>
+      <c r="B12" s="46"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="48" t="s">
-        <v>622</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>623</v>
+      <c r="A13" s="47" t="s">
+        <v>626</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>627</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="49" t="s">
-        <v>624</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>625</v>
+      <c r="A14" s="48" t="s">
+        <v>628</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>629</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="29" t="s">
-        <v>626</v>
+      <c r="B15" s="28" t="s">
+        <v>630</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="28" t="s">
-        <v>627</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>628</v>
+      <c r="A16" s="27" t="s">
+        <v>631</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>632</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="28" t="s">
-        <v>629</v>
-      </c>
-      <c r="B17" s="29" t="s">
-        <v>630</v>
+      <c r="A17" s="27" t="s">
+        <v>633</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>634</v>
       </c>
     </row>
   </sheetData>
@@ -2659,360 +2677,360 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="11" width="38.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="45" width="30.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="45" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="13" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="45" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="17" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="44" width="30.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="44" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="12" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="44" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="16" width="18.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
+        <v>596</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="15"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="16" t="s">
-        <v>593</v>
-      </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
+      <c r="A2" s="15" t="s">
+        <v>597</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="15"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="15"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="4" t="s">
-        <v>557</v>
-      </c>
-      <c r="B4" s="34" t="s">
-        <v>558</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>594</v>
+        <v>561</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>562</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>598</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="34" t="s">
-        <v>595</v>
+      <c r="E4" s="33" t="s">
+        <v>599</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="35">
+      <c r="A5" s="34">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!A2</f>
       </c>
-      <c r="B5" s="36">
+      <c r="B5" s="35">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!B2</f>
       </c>
-      <c r="C5" s="37">
+      <c r="C5" s="36">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!C2</f>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="37">
         <v>0</v>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="36">
         <f>ROUND(C5*D5,2)</f>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="34">
         <f>IF(D5&gt;&amp;apos;Produtos e Cupons&amp;apos;!$C$15,"EXCEDE (422)","ok")</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="35">
+      <c r="A6" s="34">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!A3</f>
       </c>
-      <c r="B6" s="36">
+      <c r="B6" s="35">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!B3</f>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="36">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!C3</f>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="37">
         <v>0</v>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="36">
         <f>ROUND(C6*D6,2)</f>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="34">
         <f>IF(D6&gt;&amp;apos;Produtos e Cupons&amp;apos;!$C$15,"EXCEDE (422)","ok")</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="35">
+      <c r="A7" s="34">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!A4</f>
       </c>
-      <c r="B7" s="36">
+      <c r="B7" s="35">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!B4</f>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="36">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!C4</f>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="37">
         <v>0</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="36">
         <f>ROUND(C7*D7,2)</f>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="34">
         <f>IF(D7&gt;&amp;apos;Produtos e Cupons&amp;apos;!$C$15,"EXCEDE (422)","ok")</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="35">
+      <c r="A8" s="34">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!A5</f>
       </c>
-      <c r="B8" s="36">
+      <c r="B8" s="35">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!B5</f>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="36">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!C5</f>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="37">
         <v>0</v>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="36">
         <f>ROUND(C8*D8,2)</f>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="34">
         <f>IF(D8&gt;&amp;apos;Produtos e Cupons&amp;apos;!$C$15,"EXCEDE (422)","ok")</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="35">
+      <c r="A9" s="34">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!A6</f>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="35">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!B6</f>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="36">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!C6</f>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="37">
         <v>0</v>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="36">
         <f>ROUND(C9*D9,2)</f>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="34">
         <f>IF(D9&gt;&amp;apos;Produtos e Cupons&amp;apos;!$C$15,"EXCEDE (422)","ok")</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="35">
+      <c r="A10" s="34">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!A7</f>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="35">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!B7</f>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="36">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!C7</f>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="37">
         <v>0</v>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="36">
         <f>ROUND(C10*D10,2)</f>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="34">
         <f>IF(D10&gt;&amp;apos;Produtos e Cupons&amp;apos;!$C$15,"EXCEDE (422)","ok")</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="35">
+      <c r="A11" s="34">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!A8</f>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="35">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!B8</f>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="36">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!C8</f>
       </c>
-      <c r="D11" s="38">
+      <c r="D11" s="37">
         <v>0</v>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="36">
         <f>ROUND(C11*D11,2)</f>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="34">
         <f>IF(D11&gt;&amp;apos;Produtos e Cupons&amp;apos;!$C$15,"EXCEDE (422)","ok")</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="35">
+      <c r="A12" s="34">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!A9</f>
       </c>
-      <c r="B12" s="36">
+      <c r="B12" s="35">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!B9</f>
       </c>
-      <c r="C12" s="37">
+      <c r="C12" s="36">
         <f>&amp;apos;Produtos e Cupons&amp;apos;!C9</f>
       </c>
-      <c r="D12" s="38">
+      <c r="D12" s="37">
         <v>0</v>
       </c>
-      <c r="E12" s="37">
+      <c r="E12" s="36">
         <f>ROUND(C12*D12,2)</f>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="34">
         <f>IF(D12&gt;&amp;apos;Produtos e Cupons&amp;apos;!$C$15,"EXCEDE (422)","ok")</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="3"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="15"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="28" t="s">
-        <v>560</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>573</v>
-      </c>
-      <c r="C14" s="33"/>
+      <c r="A14" s="27" t="s">
+        <v>564</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>577</v>
+      </c>
+      <c r="C14" s="32"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="15"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="33"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="15"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="28" t="s">
-        <v>597</v>
-      </c>
-      <c r="B16" s="40">
+      <c r="A16" s="27" t="s">
+        <v>601</v>
+      </c>
+      <c r="B16" s="39">
         <f>IF(B14="BEMVINDO10",&amp;apos;Produtos e Cupons&amp;apos;!F2,0)</f>
       </c>
-      <c r="C16" s="33"/>
+      <c r="C16" s="32"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="15"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="28" t="s">
-        <v>598</v>
-      </c>
-      <c r="B17" s="41">
+      <c r="A17" s="27" t="s">
+        <v>602</v>
+      </c>
+      <c r="B17" s="40">
         <f>IF(B14="BEMVINDO10","Aplicado",IF(B14="VERAO2026","Cupom expirado.",IF(B14="NAOEXISTE","Cupom inválido.","Sem cupom")))</f>
       </c>
-      <c r="C17" s="33"/>
+      <c r="C17" s="32"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="15"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="28" t="s">
-        <v>599</v>
-      </c>
-      <c r="B18" s="42">
+      <c r="A18" s="27" t="s">
+        <v>603</v>
+      </c>
+      <c r="B18" s="41">
         <f>ROUND(SUM(E5:E12),2)</f>
       </c>
-      <c r="C18" s="33"/>
+      <c r="C18" s="32"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="15"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="28" t="s">
-        <v>600</v>
-      </c>
-      <c r="B19" s="42">
+      <c r="A19" s="27" t="s">
+        <v>604</v>
+      </c>
+      <c r="B19" s="41">
         <f>ROUND(B18*B16,2)</f>
       </c>
-      <c r="C19" s="33"/>
+      <c r="C19" s="32"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="15"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="28" t="s">
-        <v>601</v>
-      </c>
-      <c r="B20" s="42">
+      <c r="A20" s="27" t="s">
+        <v>605</v>
+      </c>
+      <c r="B20" s="41">
         <f>IF(B18=0,0,IF(B18&gt;=&amp;apos;Produtos e Cupons&amp;apos;!C13,0,&amp;apos;Produtos e Cupons&amp;apos;!C14))</f>
       </c>
-      <c r="C20" s="33"/>
+      <c r="C20" s="32"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="15"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="28" t="s">
-        <v>602</v>
-      </c>
-      <c r="B21" s="42">
+      <c r="A21" s="27" t="s">
+        <v>606</v>
+      </c>
+      <c r="B21" s="41">
         <f>IF(B18=0,0,ROUND(MAX(0,&amp;apos;Produtos e Cupons&amp;apos;!C13-B18),2))</f>
       </c>
-      <c r="C21" s="33"/>
+      <c r="C21" s="32"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="15"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="43" t="s">
-        <v>603</v>
-      </c>
-      <c r="B22" s="44">
+      <c r="A22" s="42" t="s">
+        <v>607</v>
+      </c>
+      <c r="B22" s="43">
         <f>ROUND(B18-B19+B20,2)</f>
       </c>
-      <c r="C22" s="33"/>
+      <c r="C22" s="32"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="15"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="33"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="15"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="16" t="s">
-        <v>604</v>
-      </c>
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
+      <c r="A24" s="15" t="s">
+        <v>608</v>
+      </c>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="15"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="16" t="s">
-        <v>605</v>
-      </c>
-      <c r="B25" s="33"/>
-      <c r="C25" s="33"/>
+      <c r="A25" s="15" t="s">
+        <v>609</v>
+      </c>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="15"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3028,266 +3046,266 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="11" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="17" width="30.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="13" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="17" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="32" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="17" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="16" width="30.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="12" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="16" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="31" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="16" width="28.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="4" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="23" t="s">
-        <v>560</v>
-      </c>
-      <c r="F1" s="24" t="s">
-        <v>561</v>
-      </c>
-      <c r="G1" s="23" t="s">
-        <v>562</v>
+        <v>563</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="22" t="s">
+        <v>564</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>565</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>566</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="6" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>564</v>
-      </c>
-      <c r="C2" s="25">
+        <v>568</v>
+      </c>
+      <c r="C2" s="24">
         <v>59.9</v>
       </c>
-      <c r="D2" s="15"/>
+      <c r="D2" s="14"/>
       <c r="E2" s="6" t="s">
-        <v>565</v>
-      </c>
-      <c r="F2" s="26">
+        <v>569</v>
+      </c>
+      <c r="F2" s="25">
         <v>0.1</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>568</v>
-      </c>
-      <c r="C3" s="25">
+        <v>572</v>
+      </c>
+      <c r="C3" s="24">
         <v>139.9</v>
       </c>
-      <c r="D3" s="15"/>
+      <c r="D3" s="14"/>
       <c r="E3" s="6" t="s">
-        <v>569</v>
-      </c>
-      <c r="F3" s="26">
+        <v>573</v>
+      </c>
+      <c r="F3" s="25">
         <v>0.15</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="6" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>572</v>
-      </c>
-      <c r="C4" s="25">
+        <v>576</v>
+      </c>
+      <c r="C4" s="24">
         <v>189.9</v>
       </c>
-      <c r="D4" s="15"/>
+      <c r="D4" s="14"/>
       <c r="E4" s="6" t="s">
-        <v>573</v>
-      </c>
-      <c r="F4" s="26">
+        <v>577</v>
+      </c>
+      <c r="F4" s="25">
         <v>0</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="6" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>576</v>
-      </c>
-      <c r="C5" s="25">
+        <v>580</v>
+      </c>
+      <c r="C5" s="24">
         <v>49.9</v>
       </c>
-      <c r="D5" s="15"/>
+      <c r="D5" s="14"/>
       <c r="E5" s="6" t="s">
-        <v>577</v>
-      </c>
-      <c r="F5" s="26">
+        <v>581</v>
+      </c>
+      <c r="F5" s="25">
         <v>0</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>580</v>
-      </c>
-      <c r="C6" s="25">
+        <v>584</v>
+      </c>
+      <c r="C6" s="24">
         <v>100</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="15"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="6" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>582</v>
-      </c>
-      <c r="C7" s="25">
+        <v>586</v>
+      </c>
+      <c r="C7" s="24">
         <v>29.9</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="15"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="6" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>584</v>
-      </c>
-      <c r="C8" s="25">
+        <v>588</v>
+      </c>
+      <c r="C8" s="24">
         <v>229.9</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="15"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="6" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>586</v>
-      </c>
-      <c r="C9" s="25">
+        <v>590</v>
+      </c>
+      <c r="C9" s="24">
         <v>50</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="15"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3"/>
-      <c r="B10" s="15"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="15"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3"/>
-      <c r="B11" s="15"/>
+      <c r="B11" s="14"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="15"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="28" t="s">
-        <v>587</v>
-      </c>
-      <c r="B12" s="15"/>
+      <c r="A12" s="27" t="s">
+        <v>591</v>
+      </c>
+      <c r="B12" s="14"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="15"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="29" t="s">
-        <v>588</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="30">
+      <c r="A13" s="28" t="s">
+        <v>592</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="29">
         <v>200</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="15"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="29" t="s">
-        <v>589</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="30">
+      <c r="A14" s="28" t="s">
+        <v>593</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="29">
         <v>19.9</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="15"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="29" t="s">
-        <v>590</v>
-      </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="31">
+      <c r="A15" s="28" t="s">
+        <v>594</v>
+      </c>
+      <c r="B15" s="14"/>
+      <c r="C15" s="30">
         <v>5</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="15"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3"/>
-      <c r="B16" s="15"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="15"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="16" t="s">
-        <v>591</v>
-      </c>
-      <c r="B17" s="15"/>
+      <c r="A17" s="15" t="s">
+        <v>595</v>
+      </c>
+      <c r="B17" s="14"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="15"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3313,7 +3331,7 @@
     <col min="9" max="9" style="11" width="14.005" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="11" width="10.005" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="11" width="22.005" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="22" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="21" width="12.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -3321,10 +3339,10 @@
         <v>84</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>140</v>
@@ -3333,7 +3351,7 @@
         <v>90</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>92</v>
@@ -3348,15 +3366,15 @@
         <v>144</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="L1" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="L1" s="19" t="s">
         <v>145</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="8" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>12</v>
@@ -3365,28 +3383,30 @@
         <v>80</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="21"/>
+        <v>344</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="8" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>12</v>
@@ -3395,30 +3415,30 @@
         <v>37</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="I3" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>348</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="21"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="8" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>12</v>
@@ -3427,30 +3447,30 @@
         <v>37</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>353</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="21"/>
+      <c r="H4" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>12</v>
@@ -3459,30 +3479,30 @@
         <v>37</v>
       </c>
       <c r="D5" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="H5" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>353</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="21"/>
+      <c r="I5" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="8" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>12</v>
@@ -3491,26 +3511,26 @@
         <v>37</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>353</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="21"/>
+        <v>351</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="8" t="s">
@@ -3523,90 +3543,90 @@
         <v>37</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="I7" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="21"/>
+      <c r="H7" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="8" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="I8" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="21"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="8" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="21"/>
+        <v>374</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="8" t="s">
@@ -3619,28 +3639,30 @@
         <v>56</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="21"/>
+        <v>378</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="8" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>12</v>
@@ -3649,54 +3671,58 @@
         <v>80</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="21"/>
+        <v>383</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="8" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="I12" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="21"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="8" t="s">
@@ -3709,28 +3735,30 @@
         <v>80</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="21"/>
+        <v>390</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="8" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>12</v>
@@ -3739,24 +3767,26 @@
         <v>80</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="21"/>
+        <v>395</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="8" t="s">
@@ -3769,36 +3799,36 @@
         <v>99</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="I15" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="I15" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="K15" s="14" t="s">
-        <v>398</v>
-      </c>
-      <c r="L15" s="21">
+      <c r="K15" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="L15" s="20">
         <v>46244</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="8" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>13</v>
@@ -3807,36 +3837,36 @@
         <v>99</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>397</v>
-      </c>
-      <c r="I16" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>399</v>
+      </c>
+      <c r="I16" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="J16" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="K16" s="14" t="s">
-        <v>403</v>
-      </c>
-      <c r="L16" s="21">
+      <c r="K16" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="L16" s="20">
         <v>46244</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="8" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>13</v>
@@ -3845,28 +3875,30 @@
         <v>61</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="21"/>
+        <v>409</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="8" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>13</v>
@@ -3875,92 +3907,96 @@
         <v>61</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="21"/>
+        <v>413</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="8" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>417</v>
-      </c>
-      <c r="I19" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="I19" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="J19" s="14" t="s">
+      <c r="J19" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="K19" s="14" t="s">
-        <v>418</v>
-      </c>
-      <c r="L19" s="21">
+      <c r="K19" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="L19" s="20">
         <v>46244</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="8" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>423</v>
-      </c>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="21"/>
+        <v>426</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="8" t="s">
@@ -3973,28 +4009,30 @@
         <v>99</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="21"/>
+        <v>429</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="8" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>13</v>
@@ -4003,28 +4041,30 @@
         <v>99</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="21"/>
+        <v>433</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="8" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>13</v>
@@ -4033,28 +4073,30 @@
         <v>99</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="21"/>
+        <v>437</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="8" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>14</v>
@@ -4063,28 +4105,30 @@
         <v>42</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="21"/>
+        <v>441</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="8" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>14</v>
@@ -4093,28 +4137,30 @@
         <v>42</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>443</v>
-      </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="21"/>
+        <v>446</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="8" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>14</v>
@@ -4123,24 +4169,26 @@
         <v>42</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>448</v>
-      </c>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="21"/>
+        <v>451</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="8" t="s">
@@ -4153,28 +4201,30 @@
         <v>42</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="21"/>
+        <v>454</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="8" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>14</v>
@@ -4183,28 +4233,30 @@
         <v>42</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="21"/>
+        <v>458</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="8" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>14</v>
@@ -4213,58 +4265,58 @@
         <v>42</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="21"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="8" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>465</v>
-      </c>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14" t="s">
+        <v>468</v>
+      </c>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="21"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="8" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>15</v>
@@ -4273,28 +4325,30 @@
         <v>32</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="21"/>
+        <v>472</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="8" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>15</v>
@@ -4303,28 +4357,30 @@
         <v>32</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>473</v>
-      </c>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="21"/>
+        <v>476</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="8" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>15</v>
@@ -4333,28 +4389,30 @@
         <v>32</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="21"/>
+        <v>480</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="8" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>15</v>
@@ -4363,28 +4421,28 @@
         <v>32</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14" t="s">
+        <v>485</v>
+      </c>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="21"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="8" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>15</v>
@@ -4393,58 +4451,62 @@
         <v>32</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>101</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="21"/>
+        <v>489</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="8" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>490</v>
-      </c>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="21"/>
+        <v>493</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="8" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>16</v>
@@ -4453,84 +4515,90 @@
         <v>80</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="21"/>
+        <v>498</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="8" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>499</v>
-      </c>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="21"/>
+        <v>502</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="8" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J39" s="14"/>
-      <c r="K39" s="14"/>
-      <c r="L39" s="21"/>
+      <c r="H39" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="8" t="s">
@@ -4540,387 +4608,413 @@
         <v>16</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>506</v>
-      </c>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="21"/>
+        <v>509</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="8" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>509</v>
-      </c>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="21"/>
+        <v>512</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="8" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J42" s="14"/>
-      <c r="K42" s="14"/>
-      <c r="L42" s="21"/>
+        <v>516</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="8" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J43" s="14"/>
-      <c r="K43" s="14"/>
-      <c r="L43" s="21"/>
+        <v>516</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J43" s="13"/>
+      <c r="K43" s="13"/>
+      <c r="L43" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="8" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>509</v>
-      </c>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J44" s="14"/>
-      <c r="K44" s="14"/>
-      <c r="L44" s="21"/>
+        <v>512</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>521</v>
+      </c>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="8" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J45" s="14"/>
-      <c r="K45" s="14"/>
-      <c r="L45" s="21"/>
+        <v>525</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I45" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="8" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>525</v>
-      </c>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J46" s="14"/>
-      <c r="K46" s="14"/>
-      <c r="L46" s="21"/>
+        <v>529</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I46" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="J46" s="13"/>
+      <c r="K46" s="13"/>
+      <c r="L46" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="8" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J47" s="14"/>
-      <c r="K47" s="14"/>
-      <c r="L47" s="21"/>
+        <v>534</v>
+      </c>
+      <c r="H47" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I47" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="8" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>535</v>
-      </c>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="21"/>
+        <v>539</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I48" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="J48" s="13"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="8" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>540</v>
-      </c>
-      <c r="H49" s="14"/>
-      <c r="I49" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J49" s="14"/>
-      <c r="K49" s="14"/>
-      <c r="L49" s="21"/>
+        <v>544</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I49" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="J49" s="13"/>
+      <c r="K49" s="13"/>
+      <c r="L49" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="8" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>545</v>
-      </c>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J50" s="14"/>
-      <c r="K50" s="14"/>
-      <c r="L50" s="21"/>
+        <v>549</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I50" s="13" t="s">
+        <v>414</v>
+      </c>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="8" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>550</v>
-      </c>
-      <c r="H51" s="14"/>
-      <c r="I51" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J51" s="14"/>
-      <c r="K51" s="14"/>
-      <c r="L51" s="21"/>
+        <v>554</v>
+      </c>
+      <c r="H51" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I51" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="8" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D52" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>552</v>
       </c>
-      <c r="E52" s="6" t="s">
-        <v>548</v>
-      </c>
       <c r="F52" s="6" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>554</v>
-      </c>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J52" s="14"/>
-      <c r="K52" s="14"/>
-      <c r="L52" s="21"/>
+        <v>558</v>
+      </c>
+      <c r="H52" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="I52" s="13" t="s">
+        <v>346</v>
+      </c>
+      <c r="J52" s="13"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="8" t="s">
@@ -4930,7 +5024,7 @@
         <v>17</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>101</v>
@@ -4939,18 +5033,20 @@
         <v>101</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J53" s="14"/>
-      <c r="K53" s="14"/>
-      <c r="L53" s="21"/>
+        <v>560</v>
+      </c>
+      <c r="H53" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="I53" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4966,16 +5062,16 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="11" width="9.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="17" width="26.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="17" width="34.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="17" width="48.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="13" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="17" width="44.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="17" width="34.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="17" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="17" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="17" width="22.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="17" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="16" width="26.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="16" width="34.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="16" width="48.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="12" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="16" width="44.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="16" width="34.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="16" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="16" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="16" width="22.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="16" width="12.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -5032,1337 +5128,1435 @@
       <c r="F2" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
+      <c r="G2" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E3" s="7">
         <v>200</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
+        <v>156</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E4" s="7">
         <v>404</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
+        <v>161</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E5" s="7">
         <v>405</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
+        <v>166</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E6" s="7">
         <v>404</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
+        <v>171</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E7" s="7">
         <v>200</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
+        <v>176</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E8" s="7">
         <v>200</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
+        <v>180</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E9" s="7">
         <v>200</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
+        <v>184</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E10" s="7">
         <v>200</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
+        <v>188</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E11" s="7">
         <v>200</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
+        <v>192</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E12" s="7">
         <v>200</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
+        <v>196</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E13" s="7">
         <v>200</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
+        <v>200</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="8" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E14" s="7">
         <v>200</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
+        <v>204</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E15" s="7">
         <v>200</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
+        <v>208</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E16" s="7">
         <v>200</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
+        <v>212</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E17" s="7">
         <v>200</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
+        <v>216</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E18" s="7">
         <v>200</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
+        <v>220</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="8" t="s">
         <v>54</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>221</v>
+        <v>222</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>223</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
+        <v>224</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E20" s="7">
         <v>400</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
+        <v>228</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E21" s="7">
         <v>422</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
+        <v>232</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="8" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E22" s="7">
         <v>422</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
+        <v>232</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E23" s="7">
         <v>422</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
+        <v>239</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="8" t="s">
         <v>136</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E24" s="7">
         <v>422</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
+        <v>239</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E25" s="7">
         <v>422</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
+        <v>245</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E26" s="7">
         <v>422</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
+        <v>249</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E27" s="7">
         <v>422</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
+        <v>253</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E28" s="7">
         <v>422</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
+        <v>253</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="8" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E29" s="7">
         <v>422</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
+        <v>253</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="8" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E30" s="7">
         <v>422</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
+        <v>253</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="8" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E31" s="7">
         <v>422</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
+        <v>253</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E32" s="7">
         <v>200</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
+        <v>269</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="8" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E33" s="7">
         <v>422</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
+        <v>273</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E34" s="7">
         <v>200</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
+        <v>277</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E35" s="7">
         <v>201</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
+        <v>282</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E36" s="7">
         <v>201</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
+        <v>286</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E37" s="7">
         <v>422</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
+        <v>288</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E38" s="7">
         <v>422</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14"/>
+        <v>290</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E39" s="7">
         <v>422</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
-      <c r="K39" s="14"/>
+        <v>294</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E40" s="7">
         <v>422</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14"/>
+        <v>298</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E41" s="7">
         <v>422</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
+        <v>298</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="8" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E42" s="7">
         <v>201</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="14"/>
+        <v>305</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I42" s="13"/>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="8" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E43" s="7">
         <v>422</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I43" s="14"/>
-      <c r="J43" s="14"/>
-      <c r="K43" s="14"/>
+        <v>309</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13"/>
+      <c r="K43" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="8" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E44" s="7">
         <v>422</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I44" s="14"/>
-      <c r="J44" s="14"/>
-      <c r="K44" s="14"/>
+        <v>313</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="8" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E45" s="7">
         <v>422</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I45" s="14"/>
-      <c r="J45" s="14"/>
-      <c r="K45" s="14"/>
+        <v>273</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="8" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E46" s="7">
         <v>422</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14"/>
-      <c r="K46" s="14"/>
+        <v>232</v>
+      </c>
+      <c r="G46" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="8" t="s">
         <v>73</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E47" s="7">
         <v>422</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14"/>
-      <c r="K47" s="14"/>
+        <v>321</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H47" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="8" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="E48" s="19" t="s">
-        <v>324</v>
+        <v>325</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>326</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
+        <v>327</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E49" s="18" t="s">
         <v>326</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="E49" s="19" t="s">
-        <v>324</v>
-      </c>
       <c r="F49" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I49" s="14"/>
-      <c r="J49" s="14"/>
-      <c r="K49" s="14"/>
+        <v>331</v>
+      </c>
+      <c r="G49" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
+      <c r="K49" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="8" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E50" s="7">
         <v>200</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14"/>
-      <c r="K50" s="14"/>
+        <v>335</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="3"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
       <c r="E51" s="2"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="15"/>
-      <c r="K51" s="15"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
-      <c r="A52" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
+      <c r="A52" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
       <c r="E52" s="2"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="15"/>
-      <c r="K52" s="15"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6438,596 +6632,596 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="N2" s="17" t="s">
         <v>108</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="L3" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="M3" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="N3" s="13" t="s">
         <v>108</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="L4" s="14" t="s">
+      <c r="L4" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="M4" s="14" t="s">
+      <c r="M4" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="N4" s="14" t="s">
+      <c r="N4" s="13" t="s">
         <v>108</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="M5" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="N5" s="14" t="s">
+      <c r="N5" s="13" t="s">
         <v>138</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
+      <c r="A21" s="13"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
+      <c r="A22" s="13"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
+      <c r="A23" s="13"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
+      <c r="A24" s="13"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7042,13 +7236,13 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="13" width="5.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="12" width="5.005" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="11" width="38.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="17" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="17" width="44.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="17" width="44.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="17" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="17" width="34.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="16" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="16" width="44.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="16" width="44.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="16" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="16" width="34.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -7087,13 +7281,13 @@
       <c r="D2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="13" t="s">
         <v>34</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="14"/>
+      <c r="G2" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="7">
@@ -7108,13 +7302,13 @@
       <c r="D3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>39</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="14"/>
+      <c r="G3" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="7">
@@ -7129,13 +7323,13 @@
       <c r="D4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="13" t="s">
         <v>44</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="14"/>
+      <c r="G4" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="7">
@@ -7150,13 +7344,13 @@
       <c r="D5" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="13" t="s">
         <v>49</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="14"/>
+      <c r="G5" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="7">
@@ -7171,13 +7365,13 @@
       <c r="D6" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="13" t="s">
         <v>53</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="G6" s="14"/>
+      <c r="G6" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="7">
@@ -7192,13 +7386,13 @@
       <c r="D7" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="13" t="s">
         <v>58</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="14"/>
+      <c r="G7" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="7">
@@ -7213,13 +7407,13 @@
       <c r="D8" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="13" t="s">
         <v>63</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="14"/>
+      <c r="G8" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="7">
@@ -7234,13 +7428,13 @@
       <c r="D9" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="13" t="s">
         <v>68</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="14"/>
+      <c r="G9" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="7">
@@ -7255,13 +7449,13 @@
       <c r="D10" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="13" t="s">
         <v>72</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="G10" s="14"/>
+      <c r="G10" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="7">
@@ -7276,13 +7470,13 @@
       <c r="D11" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="13" t="s">
         <v>77</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="G11" s="14"/>
+      <c r="G11" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="7">
@@ -7297,33 +7491,33 @@
       <c r="D12" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="13" t="s">
         <v>81</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="14"/>
+      <c r="G12" s="13"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="2"/>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7340,11 +7534,11 @@
   <cols>
     <col min="1" max="1" style="11" width="22.005" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="12" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="13" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="13" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="12" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="12" width="12.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7574,13 +7768,13 @@
         <f>COUNTIFS(&amp;apos;Casos Manuais&amp;apos;!$B$2:$B$53,A18,&amp;apos;Casos Manuais&amp;apos;!$I$2:$I$53,"Falhou")</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="4" t="s">
         <v>18</v>
       </c>
@@ -7590,7 +7784,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="6" t="s">
         <v>4</v>
       </c>
@@ -7600,7 +7794,7 @@
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="6" t="s">
         <v>20</v>
       </c>
@@ -7610,7 +7804,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="6" t="s">
         <v>21</v>
       </c>
@@ -7620,7 +7814,7 @@
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="6" t="s">
         <v>22</v>
       </c>
@@ -7630,7 +7824,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="6" t="s">
         <v>23</v>
       </c>
